--- a/data/export/2026-10-01-operations.xlsx
+++ b/data/export/2026-10-01-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -759,32 +759,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +820,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -875,32 +883,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,17 +944,17 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -952,13 +964,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -991,32 +1007,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,33 +1068,37 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1164,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1203,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1214,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1237,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1459,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:25</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1507,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1526,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1562,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1623,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1642,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1739,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,7 +1783,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1770,35 +1794,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1855,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1874,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1899,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1975,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1994,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2002,35 +2030,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2091,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2110,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2135,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2211,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2230,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2223,7 +2255,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2234,7 +2266,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2279,7 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2257,7 +2289,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2295,12 +2327,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2346,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2350,7 +2382,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2395,7 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2373,7 +2405,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2411,12 +2443,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2462,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,7 +2498,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2511,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2489,7 +2521,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2527,12 +2559,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2578,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2614,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2675,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2694,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2730,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2791,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2810,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2846,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2907,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2926,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2962,2927 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-operations.xlsx
+++ b/data/export/2026-10-01-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AD69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -893,24 +893,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -959,22 +959,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1131,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1164,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1188,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1208,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1319,7 +1327,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1363,32 +1371,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1396,7 +1408,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1432,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1479,32 +1495,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1512,7 +1532,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1536,33 +1556,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1652,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1667,7 +1691,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1744,7 +1768,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1783,7 +1807,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1860,7 +1884,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1899,7 +1923,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1914,7 +1938,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1980,7 +2004,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2096,7 +2120,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2145,12 +2169,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2163,22 +2187,22 @@
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2216,7 +2240,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2230,7 +2254,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2260,41 +2284,45 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2327,12 +2355,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2346,7 +2374,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2371,46 +2399,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2443,12 +2475,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2462,7 +2494,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2487,46 +2519,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2559,12 +2595,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2578,7 +2614,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2603,7 +2639,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2614,35 +2650,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2675,12 +2711,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2694,7 +2730,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2719,46 +2755,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2791,12 +2831,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2810,7 +2850,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2835,7 +2875,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2846,35 +2886,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2907,12 +2947,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2926,7 +2966,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2951,7 +2991,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2962,35 +3002,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3023,12 +3063,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3042,7 +3082,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3067,18 +3107,22 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3135,7 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3101,7 +3145,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3111,40 +3155,44 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3158,7 +3206,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3168,33 +3216,37 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3259,7 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3217,7 +3269,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3227,40 +3279,44 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3274,7 +3330,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3284,33 +3340,37 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3383,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3333,7 +3393,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3343,40 +3403,44 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3390,7 +3454,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3400,17 +3464,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3420,13 +3484,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3507,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3449,7 +3517,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3459,40 +3527,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3506,7 +3578,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3516,33 +3588,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -3555,22 +3631,22 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3603,12 +3679,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3622,7 +3698,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3658,7 +3734,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3671,22 +3747,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3719,12 +3795,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3738,7 +3814,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3774,7 +3850,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3787,22 +3863,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3835,12 +3911,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3854,7 +3930,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3890,7 +3966,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3979,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3913,7 +3989,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3951,12 +4027,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3970,7 +4046,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4006,7 +4082,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4095,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4029,7 +4105,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4067,12 +4143,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4086,7 +4162,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4122,7 +4198,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4211,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4145,7 +4221,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4183,12 +4259,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4202,7 +4278,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4238,7 +4314,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4327,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4261,7 +4337,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4299,12 +4375,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4318,7 +4394,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4354,7 +4430,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4367,22 +4443,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4415,12 +4491,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4434,7 +4510,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4470,35 +4546,35 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4531,12 +4607,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4550,7 +4626,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4575,7 +4651,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4586,77 +4662,73 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4670,7 +4742,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4680,65 +4752,61 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4839,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4858,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4815,7 +4883,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4826,77 +4894,73 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4910,7 +4974,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4920,17 +4984,17 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4940,45 +5004,41 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5011,12 +5071,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5030,7 +5090,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5066,35 +5126,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5127,12 +5187,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5146,7 +5206,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5182,35 +5242,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5243,12 +5303,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5262,7 +5322,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5298,35 +5358,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5359,12 +5419,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5378,7 +5438,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5403,7 +5463,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5414,35 +5474,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5475,12 +5535,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5494,7 +5554,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5530,35 +5590,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5591,12 +5651,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5610,7 +5670,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5646,35 +5706,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5707,12 +5767,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5726,7 +5786,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5751,50 +5811,46 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5827,12 +5883,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5846,7 +5902,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5871,7 +5927,7 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -5882,7 +5938,2755 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>4/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-operations.xlsx
+++ b/data/export/2026-10-01-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD69"/>
+  <dimension ref="A1:AD87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -720,13 +720,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -796,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -850,7 +854,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -920,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -959,22 +963,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1083,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1168,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,14 +1211,14 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -1222,7 +1226,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1327,7 +1331,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1408,7 +1412,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1532,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1586,7 +1590,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1656,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1735,32 +1739,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1768,7 +1776,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1792,17 +1800,17 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1812,13 +1820,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1896,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1938,7 +1950,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1971,32 +1983,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2004,7 +2020,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2028,33 +2044,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2140,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2159,7 +2179,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2207,32 +2227,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2240,7 +2264,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2264,37 +2288,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2327,32 +2351,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2360,7 +2388,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2384,29 +2412,29 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -2414,7 +2442,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2508,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2600,7 +2628,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2639,7 +2667,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2716,7 +2744,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2770,7 +2798,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2864,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2952,7 +2980,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2996,13 +3024,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -3015,22 +3047,22 @@
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3063,12 +3095,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3082,7 +3114,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3107,7 +3139,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3117,82 +3149,78 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3206,7 +3234,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3216,22 +3244,22 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3241,82 +3269,78 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3330,7 +3354,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3340,107 +3364,103 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3454,7 +3474,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3464,107 +3484,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3578,7 +3594,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3588,65 +3604,61 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>137.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3679,12 +3691,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3698,7 +3710,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3723,18 +3735,22 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3747,52 +3763,56 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3800,7 +3820,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3814,7 +3834,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3824,33 +3844,37 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3863,60 +3887,64 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3930,7 +3958,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3940,33 +3968,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3979,7 +4011,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3989,7 +4021,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3999,40 +4031,44 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4046,7 +4082,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4056,33 +4092,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4135,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4105,7 +4145,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4115,40 +4155,44 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4162,7 +4206,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4172,33 +4216,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4259,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4221,7 +4269,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4259,12 +4307,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4278,7 +4326,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4303,7 +4351,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4314,7 +4362,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4375,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4337,7 +4385,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4347,40 +4395,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4394,7 +4446,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4404,33 +4456,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4443,60 +4499,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4510,7 +4570,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4520,33 +4580,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4623,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4569,7 +4633,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4579,40 +4643,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4626,7 +4694,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4636,17 +4704,17 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4656,13 +4724,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4747,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4685,7 +4757,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4695,40 +4767,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4742,7 +4818,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4752,33 +4828,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4871,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4801,7 +4881,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4811,40 +4891,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4858,7 +4942,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4868,17 +4952,17 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4888,13 +4972,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4995,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4917,7 +5005,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4927,40 +5015,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4974,7 +5066,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4984,33 +5076,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -5023,22 +5119,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5071,12 +5167,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5090,7 +5186,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5126,7 +5222,7 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5139,22 +5235,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5187,12 +5283,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5206,7 +5302,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5242,7 +5338,7 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5255,32 +5351,32 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq51，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5303,12 +5399,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5316,13 +5412,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
       <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5358,7 +5466,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5371,22 +5479,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5419,12 +5527,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5438,7 +5546,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5474,7 +5582,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5487,22 +5595,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5535,12 +5643,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5554,7 +5662,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5590,7 +5698,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5603,22 +5711,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5651,12 +5759,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5670,7 +5778,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5706,7 +5814,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5827,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5729,7 +5837,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5767,12 +5875,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5786,7 +5894,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5822,7 +5930,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5943,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5845,7 +5953,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5883,12 +5991,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5902,7 +6010,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5938,7 +6046,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5951,22 +6059,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5999,12 +6107,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6018,7 +6126,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6054,7 +6162,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6067,22 +6175,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6115,12 +6223,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6134,7 +6242,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6170,7 +6278,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6291,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6193,7 +6301,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6236,7 +6344,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6250,7 +6358,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6275,22 +6383,18 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6303,22 +6407,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6351,12 +6455,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6370,7 +6474,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6395,22 +6499,18 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6523,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6433,7 +6533,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6476,7 +6576,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6490,7 +6590,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6515,50 +6615,46 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>137.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6591,12 +6687,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6610,7 +6706,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6635,7 +6731,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6646,77 +6742,73 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6730,7 +6822,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6740,107 +6832,99 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6854,7 +6938,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6864,17 +6948,17 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6889,82 +6973,78 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6978,7 +7058,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6988,17 +7068,17 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7013,82 +7093,78 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7102,7 +7178,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7112,17 +7188,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7137,82 +7213,78 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7226,7 +7298,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7236,17 +7308,17 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7261,82 +7333,78 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7350,7 +7418,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7360,65 +7428,65 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7451,12 +7519,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7470,7 +7538,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7506,35 +7574,35 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7567,12 +7635,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7586,7 +7654,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7611,46 +7679,50 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7683,12 +7755,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7702,7 +7774,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7727,46 +7799,50 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7799,12 +7875,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7818,7 +7894,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7843,50 +7919,46 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7919,12 +7991,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7938,7 +8010,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7973,12 +8045,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -7991,22 +8063,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8039,12 +8111,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8058,7 +8130,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8083,18 +8155,22 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8107,52 +8183,56 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8160,7 +8240,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8174,7 +8254,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8184,17 +8264,17 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8214,7 +8294,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8227,52 +8307,56 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8280,7 +8364,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8294,7 +8378,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8304,17 +8388,17 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8329,12 +8413,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8347,60 +8431,64 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8414,7 +8502,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8424,33 +8512,37 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8555,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8473,7 +8565,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8483,32 +8575,36 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8516,7 +8612,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8530,7 +8626,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8540,17 +8636,17 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8565,12 +8661,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8679,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8593,7 +8689,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8603,40 +8699,44 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8650,43 +8750,2203 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W69" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X69" s="2" t="inlineStr">
+      <c r="X80" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y69" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z69" s="2" t="inlineStr">
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC69" s="2" t="inlineStr"/>
-      <c r="AD69" s="2" t="inlineStr">
-        <is>
-          <t>—/12</t>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-operations.xlsx
+++ b/data/export/2026-10-01-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD87"/>
+  <dimension ref="A1:AD93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1336,13 +1336,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1456,17 +1460,17 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1575,7 +1579,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1590,7 +1594,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1695,7 +1699,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1776,7 +1780,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1896,7 +1900,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2020,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2074,7 +2078,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2194,7 +2198,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2268,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2318,7 +2322,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -2361,24 +2365,24 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2388,7 +2392,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2437,12 +2441,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2475,32 +2479,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2508,7 +2516,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2532,17 +2540,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2552,17 +2560,17 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -2595,32 +2603,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2628,7 +2640,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2652,17 +2664,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2672,13 +2684,17 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2760,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2783,7 +2799,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2798,7 +2814,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2880,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2903,7 +2919,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2980,7 +2996,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3100,7 +3116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3154,7 +3170,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3236,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3340,7 +3356,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3394,7 +3410,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3476,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3514,7 +3530,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3596,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3624,13 +3640,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3716,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3745,82 +3765,78 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3834,7 +3850,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3844,107 +3860,99 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3958,7 +3966,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3968,22 +3976,22 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3993,12 +4001,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4019,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4021,7 +4029,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4041,12 +4049,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
@@ -4068,7 +4076,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4082,7 +4090,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4117,12 +4125,12 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4143,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4145,7 +4153,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4165,7 +4173,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -4177,12 +4185,12 @@
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4192,7 +4200,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4206,7 +4214,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4246,7 +4254,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4267,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4269,7 +4277,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4279,32 +4287,36 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4312,7 +4324,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4326,7 +4338,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4336,17 +4348,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4356,13 +4368,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4391,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4385,7 +4401,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4405,24 +4421,24 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4432,7 +4448,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4446,7 +4462,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4481,12 +4497,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4515,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4509,7 +4525,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4519,44 +4535,40 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4570,7 +4582,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4580,17 +4592,17 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4600,17 +4612,13 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4623,24 +4631,24 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4653,12 +4661,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
@@ -4675,12 +4683,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4694,7 +4702,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4719,22 +4727,22 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4747,24 +4755,24 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4777,34 +4785,34 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4818,7 +4826,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4853,12 +4861,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4879,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4881,7 +4889,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4901,7 +4909,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4913,22 +4921,22 @@
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4942,7 +4950,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4967,7 +4975,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4995,7 +5003,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5005,7 +5013,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5025,34 +5033,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5066,7 +5074,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5101,12 +5109,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -5119,55 +5127,59 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5186,7 +5198,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5196,17 +5208,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5216,13 +5228,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -5235,60 +5251,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5302,7 +5322,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5312,33 +5332,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5375,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5361,7 +5385,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5371,40 +5395,44 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq51，推进10站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5412,25 +5440,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>物理seq23（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5440,33 +5456,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5499,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5489,7 +5509,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5499,40 +5519,44 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5546,7 +5570,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5556,17 +5580,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5576,13 +5600,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5623,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5605,7 +5633,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5615,12 +5643,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq55，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5643,12 +5671,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5656,13 +5684,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5711,7 +5751,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5721,7 +5761,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5759,12 +5799,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5778,7 +5818,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5827,7 +5867,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5837,7 +5877,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5875,12 +5915,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5894,7 +5934,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5943,7 +5983,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5953,7 +5993,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5991,12 +6031,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6010,7 +6050,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6059,7 +6099,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6069,7 +6109,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6107,12 +6147,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6126,7 +6166,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6175,7 +6215,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6185,7 +6225,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6223,12 +6263,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6242,7 +6282,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6291,7 +6331,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6301,7 +6341,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6339,12 +6379,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6358,7 +6398,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6407,22 +6447,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6455,12 +6495,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6474,7 +6514,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6523,22 +6563,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6576,7 +6616,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6590,7 +6630,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6639,22 +6679,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6687,12 +6727,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6706,7 +6746,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6755,22 +6795,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6808,7 +6848,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6822,7 +6862,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6871,22 +6911,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6924,7 +6964,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6938,7 +6978,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6963,22 +7003,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6991,22 +7027,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7044,7 +7080,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7058,7 +7094,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7083,22 +7119,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7111,22 +7143,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7164,7 +7196,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7178,7 +7210,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7213,12 +7245,12 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -7231,22 +7263,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7284,7 +7316,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7298,7 +7330,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7333,12 +7365,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7383,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7361,7 +7393,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7404,7 +7436,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7418,7 +7450,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7453,12 +7485,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7503,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7481,7 +7513,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7524,7 +7556,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7538,7 +7570,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7568,13 +7600,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -7587,22 +7623,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7635,12 +7671,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7654,7 +7690,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7689,12 +7725,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -7707,22 +7743,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7755,12 +7791,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7774,7 +7810,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7804,17 +7840,13 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7859,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A79307D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7837,7 +7869,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7875,12 +7907,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7894,7 +7926,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7919,18 +7951,22 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7979,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7953,7 +7989,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7991,12 +8027,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8010,7 +8046,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8045,40 +8081,40 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8111,12 +8147,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8130,7 +8166,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8155,92 +8191,84 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8254,7 +8282,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8264,17 +8292,17 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8289,82 +8317,78 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8378,7 +8402,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8388,17 +8412,17 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8413,82 +8437,78 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8502,7 +8522,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8512,17 +8532,17 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8537,12 +8557,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8575,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8565,7 +8585,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8575,36 +8595,32 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8612,7 +8628,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8626,7 +8642,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8636,22 +8652,22 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8661,7 +8677,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -8679,7 +8695,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8689,7 +8705,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8709,19 +8725,19 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8731,12 +8747,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8750,7 +8766,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8775,7 +8791,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8785,12 +8801,12 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8819,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8813,7 +8829,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8833,12 +8849,12 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
@@ -8855,12 +8871,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8874,7 +8890,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8899,22 +8915,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8943,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8937,7 +8953,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8957,34 +8973,34 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8998,7 +9014,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9023,7 +9039,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -9033,12 +9049,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9067,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9061,7 +9077,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9081,12 +9097,12 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
@@ -9103,12 +9119,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9122,7 +9138,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9157,12 +9173,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9191,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9185,7 +9201,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9205,34 +9221,34 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9246,7 +9262,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9281,12 +9297,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9315,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9309,7 +9325,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9319,32 +9335,36 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9352,7 +9372,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9366,7 +9386,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9376,17 +9396,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9401,12 +9421,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9439,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9429,7 +9449,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9439,32 +9459,36 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9472,7 +9496,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9486,7 +9510,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9496,22 +9520,22 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
@@ -9521,12 +9545,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9539,60 +9563,64 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9606,7 +9634,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9616,33 +9644,37 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9655,60 +9687,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9722,7 +9758,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9732,17 +9768,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9762,7 +9798,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9775,22 +9811,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9823,12 +9859,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9842,7 +9878,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9867,7 +9903,7 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -9877,12 +9913,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9895,60 +9931,64 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9962,7 +10002,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9972,33 +10012,37 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10011,22 +10055,22 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -10059,12 +10103,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10078,7 +10122,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10103,22 +10147,18 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -10131,22 +10171,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -10179,12 +10219,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10198,7 +10238,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10223,18 +10263,22 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB81" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10291,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -10257,7 +10301,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10295,12 +10339,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10314,7 +10358,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10339,18 +10383,22 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10411,7 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10373,7 +10421,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10411,12 +10459,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10430,7 +10478,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10479,22 +10527,22 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -10527,12 +10575,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10546,7 +10594,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10581,7 +10629,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
@@ -10599,7 +10647,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10609,7 +10657,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10647,12 +10695,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10666,7 +10714,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10691,22 +10739,18 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC85" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -10719,22 +10763,22 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10767,12 +10811,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10786,7 +10830,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10811,22 +10855,18 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -10839,7 +10879,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -10849,7 +10889,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10887,12 +10927,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10906,47 +10946,763 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="W87" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X87" s="2" t="inlineStr">
+      <c r="X92" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y87" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z87" s="2" t="inlineStr">
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
+      <c r="AA92" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB87" s="2" t="inlineStr">
+      <c r="AB92" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC87" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="AD87" s="2" t="inlineStr">
-        <is>
-          <t>9/14</t>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-operations.xlsx
+++ b/data/export/2026-10-01-operations.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6404,12 +6404,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8128,12 +8128,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8500,12 +8500,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8813,12 +8813,12 @@
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8915,32 +8915,36 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8948,7 +8952,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8972,17 +8976,17 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8992,12 +8996,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
@@ -9045,24 +9049,24 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -9072,7 +9076,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9121,12 +9125,12 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -9159,32 +9163,36 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9192,7 +9200,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9216,17 +9224,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -9236,12 +9244,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9279,32 +9287,36 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9312,7 +9324,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9336,17 +9348,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9356,12 +9368,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
@@ -9432,7 +9444,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9476,12 +9488,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9804,7 +9816,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9848,17 +9860,17 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10308,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10668,7 +10680,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10792,7 +10804,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10836,17 +10848,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10928,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10960,17 +10972,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11172,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11292,7 +11304,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11416,7 +11428,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11460,17 +11472,17 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11676,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11718,7 +11730,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11800,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11908,7 +11920,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12152,7 +12164,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12201,12 +12213,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12288,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12648,7 +12660,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12697,12 +12709,12 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13156,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13188,17 +13200,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -13516,7 +13528,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13888,7 +13900,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13932,17 +13944,17 @@
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -14136,7 +14148,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14260,7 +14272,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14304,17 +14316,17 @@
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -14508,7 +14520,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14552,17 +14564,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14644,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14756,7 +14768,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14810,7 +14822,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15016,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15128,7 +15140,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15376,7 +15388,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -16624,7 +16636,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16872,7 +16884,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16916,17 +16928,17 @@
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -17120,7 +17132,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -18368,7 +18380,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18412,17 +18424,17 @@
       </c>
       <c r="AB145" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -18492,7 +18504,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18541,12 +18553,12 @@
       </c>
       <c r="AC146" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -18616,7 +18628,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18665,12 +18677,12 @@
       </c>
       <c r="AC147" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -18736,7 +18748,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18780,17 +18792,17 @@
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC148" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -18860,7 +18872,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18984,7 +18996,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19038,7 +19050,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -19108,7 +19120,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19152,17 +19164,17 @@
       </c>
       <c r="AB151" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC151" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -19228,7 +19240,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19352,7 +19364,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19476,7 +19488,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19968,7 +19980,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20960,7 +20972,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21057,24 +21069,24 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr"/>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
@@ -21084,7 +21096,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21133,12 +21145,12 @@
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -21171,32 +21183,36 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr"/>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N168" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -21204,7 +21220,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21228,17 +21244,17 @@
       </c>
       <c r="X168" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z168" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA168" s="2" t="inlineStr">
@@ -21248,17 +21264,17 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -21301,24 +21317,24 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr"/>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
@@ -21328,7 +21344,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21377,12 +21393,12 @@
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -21415,32 +21431,36 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr"/>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N170" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -21448,7 +21468,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21472,17 +21492,17 @@
       </c>
       <c r="X170" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y170" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z170" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA170" s="2" t="inlineStr">
@@ -21492,17 +21512,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -21535,12 +21555,12 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
@@ -21568,7 +21588,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21576,10 +21596,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R171" s="2" t="inlineStr"/>
-      <c r="S171" s="2" t="inlineStr"/>
-      <c r="T171" s="2" t="inlineStr"/>
-      <c r="U171" s="2" t="inlineStr"/>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V171" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -21655,32 +21691,36 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N172" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -21688,7 +21728,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21712,17 +21752,17 @@
       </c>
       <c r="X172" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA172" s="2" t="inlineStr">
@@ -21732,17 +21772,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -21775,32 +21815,36 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -21808,7 +21852,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21832,17 +21876,17 @@
       </c>
       <c r="X173" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z173" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA173" s="2" t="inlineStr">
@@ -21852,17 +21896,17 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21972,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22048,7 +22092,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22168,7 +22212,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22222,7 +22266,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -22288,7 +22332,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22408,7 +22452,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22528,7 +22572,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22648,7 +22692,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22946,7 +22990,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23114,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -23318,7 +23362,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -23388,7 +23432,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23437,12 +23481,12 @@
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -23566,7 +23610,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -23760,7 +23804,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23814,7 +23858,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23928,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24062,7 +24106,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -24186,7 +24230,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -24252,7 +24296,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24296,17 +24340,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -24550,7 +24594,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24718,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -24740,7 +24784,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24789,12 +24833,12 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -24864,7 +24908,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24908,17 +24952,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -24988,7 +25032,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25032,17 +25076,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -25286,7 +25330,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -25356,7 +25400,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25410,7 +25454,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -25658,7 +25702,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -25728,7 +25772,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -26026,7 +26070,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -26146,7 +26190,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -26216,7 +26260,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26260,17 +26304,17 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -26340,7 +26384,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26389,12 +26433,12 @@
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -26588,7 +26632,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26632,17 +26676,17 @@
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -26836,7 +26880,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26880,17 +26924,17 @@
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -26960,7 +27004,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27138,7 +27182,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -27262,7 +27306,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -27332,7 +27376,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27376,17 +27420,17 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -27506,7 +27550,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -27576,7 +27620,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27620,17 +27664,17 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27798,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -27824,7 +27868,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27868,17 +27912,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -28002,7 +28046,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -28126,7 +28170,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -28192,7 +28236,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28370,7 +28414,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -28618,7 +28662,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -28688,7 +28732,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28742,7 +28786,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -28866,7 +28910,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -28936,7 +28980,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29060,7 +29104,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29238,7 +29282,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -29362,7 +29406,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29600,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29600,17 +29644,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29724,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29734,7 +29778,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -29804,7 +29848,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29848,17 +29892,17 @@
       </c>
       <c r="AB238" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC238" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -29928,7 +29972,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -30106,7 +30150,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -30176,7 +30220,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30225,12 +30269,12 @@
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -30354,7 +30398,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -30478,7 +30522,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -30544,7 +30588,7 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
@@ -30588,17 +30632,17 @@
       </c>
       <c r="AB244" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC244" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -30668,7 +30712,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30846,7 +30890,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -30966,7 +31010,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -31036,7 +31080,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31080,17 +31124,17 @@
       </c>
       <c r="AB248" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -31284,7 +31328,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -31328,17 +31372,17 @@
       </c>
       <c r="AB250" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31630,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -31656,7 +31700,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31705,12 +31749,12 @@
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31824,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -31834,7 +31878,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -31958,7 +32002,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -32028,7 +32072,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q256" s="2" t="inlineStr">
@@ -32072,17 +32116,17 @@
       </c>
       <c r="AB256" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC256" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -32152,7 +32196,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32276,7 +32320,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32454,7 +32498,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -32574,7 +32618,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -32694,7 +32738,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -32764,7 +32808,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32808,17 +32852,17 @@
       </c>
       <c r="AB262" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -33008,7 +33052,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33052,17 +33096,17 @@
       </c>
       <c r="AB264" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -33310,7 +33354,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -33380,7 +33424,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33434,7 +33478,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -33477,12 +33521,12 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K268" s="2" t="inlineStr"/>
@@ -33504,7 +33548,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33553,12 +33597,12 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -33678,7 +33722,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33748,7 +33792,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33955,32 +33999,36 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr"/>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N272" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N272" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O272" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -33988,7 +34036,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34012,17 +34060,17 @@
       </c>
       <c r="X272" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y272" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z272" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA272" s="2" t="inlineStr">
@@ -34032,17 +34080,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34156,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34195,32 +34243,36 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr"/>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N274" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O274" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -34228,7 +34280,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34252,17 +34304,17 @@
       </c>
       <c r="X274" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z274" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA274" s="2" t="inlineStr">
@@ -34272,17 +34324,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -34315,32 +34367,36 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr"/>
       <c r="M275" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N275" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N275" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O275" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -34348,7 +34404,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34372,17 +34428,17 @@
       </c>
       <c r="X275" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y275" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z275" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA275" s="2" t="inlineStr">
@@ -34392,17 +34448,17 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -34468,7 +34524,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34512,17 +34568,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34588,7 +34644,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
